--- a/naver-place-crawler/results_health/송파_PT.xlsx
+++ b/naver-place-crawler/results_health/송파_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>매직바디짐</t>
+          <t>모어핏 여성전용 PT&amp;Pilates 송파나루점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>moonsung84@naver.com</t>
+          <t>more_fit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1482-8806</t>
+          <t>0507-1395-4335</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로7길 41 NS파인트리 오피스텔 상가 4층 402호</t>
+          <t>서울 송파구 백제고분로 433 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/moonsung84</t>
+          <t>https://blog.naver.com/more_fit</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cku7</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="Q2" t="n">
-        <v>186</v>
+        <v>391</v>
       </c>
       <c r="R2" t="n">
-        <v>337</v>
+        <v>594</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1869534429</t>
+          <t>1034357419</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1869534429</t>
+          <t>https://m.place.naver.com/place/1034357419</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>슈나이더짐 PT&amp;필라테스</t>
+          <t>씨엘필라테스 잠실새내점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>schneider-gym@naver.com</t>
+          <t>clpilates6@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1379-6625</t>
+          <t>0507-1336-6376</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
+          <t>서울 송파구 백제고분로7길 57 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/schneider-gym</t>
+          <t>https://blog.naver.com/clpilates6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40v0r</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>408</v>
+        <v>734</v>
       </c>
       <c r="Q3" t="n">
-        <v>1137</v>
+        <v>1469</v>
       </c>
       <c r="R3" t="n">
-        <v>1545</v>
+        <v>2203</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>37562355</t>
+          <t>1469498219</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37562355</t>
+          <t>https://m.place.naver.com/place/1469498219</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>발란아워 GYM&amp;PT 잠실점</t>
+          <t>슈나이더짐 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>balanour@naver.com</t>
+          <t>schneider-gym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1348-9763</t>
+          <t>0507-1379-6625</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
+          <t>서울특별시 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balanour</t>
+          <t>https://blog.naver.com/schneider-gym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>305</v>
+        <v>408</v>
       </c>
       <c r="Q4" t="n">
-        <v>619</v>
+        <v>1137</v>
       </c>
       <c r="R4" t="n">
-        <v>924</v>
+        <v>1545</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1805832183</t>
+          <t>37562355</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805832183</t>
+          <t>https://m.place.naver.com/place/37562355</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바디랩그룹트레이닝&amp;PT</t>
+          <t>발란아워 GYM&amp;PT 잠실점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bodylab3594@naver.com</t>
+          <t>balanour@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1471-0732</t>
+          <t>0507-1348-9763</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 올림픽로35길 104 장미전철상가 4층 바디랩그룹트레이닝&amp;PT</t>
+          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodylab3594/223941245210</t>
+          <t>https://blog.naver.com/balanour</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>363</v>
+        <v>305</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>619</v>
       </c>
       <c r="R5" t="n">
-        <v>737</v>
+        <v>924</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1700758796</t>
+          <t>1805832183</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700758796</t>
+          <t>https://m.place.naver.com/place/1805832183</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1000,10 +1008,10 @@
         <v>210</v>
       </c>
       <c r="Q6" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="R6" t="n">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1034,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>앵글짐&amp;프리모필라테스</t>
+          <t>바디랩그룹트레이닝&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>anglegym@naver.com</t>
+          <t>bodylab3594@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1362-3197</t>
+          <t>0507-1471-0732</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
+          <t>서울특별시 송파구 올림픽로35길 104 장미전철상가 4층 바디랩그룹트레이닝&amp;PT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anglegym_primopilates/</t>
+          <t>https://blog.naver.com/bodylab3594/223941245210</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1079,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>409</v>
+        <v>363</v>
       </c>
       <c r="Q7" t="n">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="R7" t="n">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1114,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1884191160</t>
+          <t>1700758796</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884191160</t>
+          <t>https://m.place.naver.com/place/1700758796</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,34 +1131,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>투엑스휘트니스 잠실점</t>
+          <t>앵글짐&amp;프리모필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hik8891@naver.com</t>
+          <t>anglegym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1447-9811</t>
+          <t>0507-1362-3197</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 올림픽로 145 리센츠 상가 B1층 잠실새내역 8번출구</t>
+          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/2x_fitness_jamsil_/</t>
+          <t>https://www.instagram.com/anglegym_primopilates/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1742</v>
+        <v>409</v>
       </c>
       <c r="Q8" t="n">
-        <v>180</v>
+        <v>342</v>
       </c>
       <c r="R8" t="n">
-        <v>1922</v>
+        <v>751</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1208,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>34897496</t>
+          <t>1884191160</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34897496</t>
+          <t>https://m.place.naver.com/place/1884191160</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1225,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>요가랩 잠실센터</t>
+          <t>투엑스휘트니스 잠실점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>yogalab_jamsil@naver.com</t>
+          <t>hik8891@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1347-9642</t>
+          <t>0507-1447-9811</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
+          <t>서울특별시 송파구 올림픽로 145 리센츠 상가 B1층 잠실새내역 8번출구</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yogalab_jamsil</t>
+          <t>https://www.instagram.com/2x_fitness_jamsil_/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,19 +1267,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43xv0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>163</v>
+        <v>1744</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="R9" t="n">
-        <v>183</v>
+        <v>1924</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1302,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>38531279</t>
+          <t>34897496</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38531279</t>
+          <t>https://m.place.naver.com/place/34897496</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1315,34 +1319,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더메이트 PT 문정점</t>
+          <t>요가랩 잠실센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>themate1907@naver.com</t>
+          <t>yogalab_jamsil@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1433-1907</t>
+          <t>0507-1347-9642</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 법원로4길 10 힐스테이트에코문정 2층 215,218,219호</t>
+          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/themate1907</t>
+          <t>https://blog.naver.com/yogalab_jamsil</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1362,10 +1366,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43xv0</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="Q10" t="n">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1400,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1832145060</t>
+          <t>38531279</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1832145060</t>
+          <t>https://m.place.naver.com/place/38531279</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1569,13 +1577,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q12" t="n">
         <v>333</v>
       </c>
       <c r="R12" t="n">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/송파_PT.xlsx
+++ b/naver-place-crawler/results_health/송파_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q2" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="R2" t="n">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,41 +650,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨엘필라테스 잠실새내점</t>
+          <t>슈나이더짐 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>clpilates6@naver.com</t>
+          <t>schneider-gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1336-6376</t>
+          <t>0507-1379-6625</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 송파구 백제고분로7길 57 7층</t>
+          <t>서울특별시 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/clpilates6</t>
+          <t>https://blog.naver.com/schneider-gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40v0r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>734</v>
+        <v>408</v>
       </c>
       <c r="Q3" t="n">
-        <v>1469</v>
+        <v>1137</v>
       </c>
       <c r="R3" t="n">
-        <v>2203</v>
+        <v>1545</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1469498219</t>
+          <t>37562355</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1469498219</t>
+          <t>https://m.place.naver.com/place/37562355</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>슈나이더짐 PT&amp;필라테스</t>
+          <t>발란아워 GYM&amp;PT 잠실점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>schneider-gym@naver.com</t>
+          <t>balanour@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1379-6625</t>
+          <t>0507-1348-9763</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
+          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/schneider-gym</t>
+          <t>https://blog.naver.com/balanour</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>408</v>
+        <v>308</v>
       </c>
       <c r="Q4" t="n">
-        <v>1137</v>
+        <v>621</v>
       </c>
       <c r="R4" t="n">
-        <v>1545</v>
+        <v>929</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>37562355</t>
+          <t>1805832183</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37562355</t>
+          <t>https://m.place.naver.com/place/1805832183</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -854,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>발란아워 GYM&amp;PT 잠실점</t>
+          <t>데일리피트니스 PT 개롱역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>balanour@naver.com</t>
+          <t>dailyfitness_1st@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1348-9763</t>
+          <t>0507-1402-1181</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
+          <t>서울특별시 송파구 동남로 202 지하1층 데일리피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balanour</t>
+          <t>https://blog.naver.com/dailyfitness_1st</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -911,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>305</v>
+        <v>211</v>
       </c>
       <c r="Q5" t="n">
-        <v>619</v>
+        <v>571</v>
       </c>
       <c r="R5" t="n">
-        <v>924</v>
+        <v>782</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1805832183</t>
+          <t>1135202102</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805832183</t>
+          <t>https://m.place.naver.com/place/1135202102</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -948,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>데일리피트니스 PT 개롱역점</t>
+          <t>피지오로직 재활PT&amp;트레이닝센터</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dailyfitness_1st@naver.com</t>
+          <t>physio_logic_@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1402-1181</t>
+          <t>0507-1357-7813</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 동남로 202 지하1층 데일리피트니스</t>
+          <t>서울특별시 송파구 가락로 99 601호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailyfitness_1st</t>
+          <t>https://blog.naver.com/physio_logic_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1005,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="Q6" t="n">
-        <v>551</v>
+        <v>302</v>
       </c>
       <c r="R6" t="n">
-        <v>761</v>
+        <v>383</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1135202102</t>
+          <t>2067533579</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135202102</t>
+          <t>https://m.place.naver.com/place/2067533579</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1042,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바디랩그룹트레이닝&amp;PT</t>
+          <t>앵글짐&amp;프리모필라테스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodylab3594@naver.com</t>
+          <t>anglegym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1471-0732</t>
+          <t>0507-1362-3197</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 올림픽로35길 104 장미전철상가 4층 바디랩그룹트레이닝&amp;PT</t>
+          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodylab3594/223941245210</t>
+          <t>https://www.instagram.com/anglegym_primopilates/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1079,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1099,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="Q7" t="n">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="R7" t="n">
-        <v>738</v>
+        <v>751</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,51 +1110,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1700758796</t>
+          <t>1884191160</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700758796</t>
+          <t>https://m.place.naver.com/place/1884191160</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>앵글짐&amp;프리모필라테스</t>
+          <t>요가랩 잠실센터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>anglegym@naver.com</t>
+          <t>yogalab_jamsil@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1362-3197</t>
+          <t>0507-1347-9642</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
+          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anglegym_primopilates/</t>
+          <t>https://blog.naver.com/yogalab_jamsil</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1173,15 +1169,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43xv0</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>409</v>
+        <v>163</v>
       </c>
       <c r="Q8" t="n">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
-        <v>751</v>
+        <v>183</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1884191160</t>
+          <t>38531279</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884191160</t>
+          <t>https://m.place.naver.com/place/38531279</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1230,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>투엑스휘트니스 잠실점</t>
+          <t>짐타임 송파나루역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hik8891@naver.com</t>
+          <t>gymtime02@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1447-9811</t>
+          <t>0507-1409-7458</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 올림픽로 145 리센츠 상가 B1층 잠실새내역 8번출구</t>
+          <t>서울특별시 송파구 백제고분로 460 B1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/2x_fitness_jamsil_/</t>
+          <t>https://blog.naver.com/gymtime02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1278,7 +1278,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1744</v>
+        <v>2759</v>
       </c>
       <c r="Q9" t="n">
-        <v>180</v>
+        <v>386</v>
       </c>
       <c r="R9" t="n">
-        <v>1924</v>
+        <v>3145</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,51 +1302,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>34897496</t>
+          <t>1324257365</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34897496</t>
+          <t>https://m.place.naver.com/place/1324257365</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>요가랩 잠실센터</t>
+          <t>짐퍼스트 헬스&amp;PT 문정역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yogalab_jamsil@naver.com</t>
+          <t>cjh23032@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1347-9642</t>
+          <t>0507-1371-9308</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
+          <t>서울특별시 송파구 법원로 114 엠스테이트 빌딩 B동 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yogalab_jamsil</t>
+          <t>https://blog.naver.com/cjh23032</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1366,14 +1366,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43xv0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1385,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>163</v>
+        <v>697</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>895</v>
       </c>
       <c r="R10" t="n">
-        <v>183</v>
+        <v>1592</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,56 +1396,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38531279</t>
+          <t>313691459</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38531279</t>
+          <t>https://m.place.naver.com/place/313691459</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐구석피티 위례점</t>
+          <t>에이블짐 잠실역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gymgooseok1@naver.com</t>
+          <t>ablegym38@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1465-0342</t>
+          <t>0507-1360-6852</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 위례광장로 200 10층 제1002호, 제1003호</t>
+          <t>서울특별시 송파구 올림픽로35가길 11 지하1층 001호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymgooseok1</t>
+          <t>https://ablegym-jamsil-vrtour.netlify.app/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1459,7 +1455,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1479,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>196</v>
+        <v>1439</v>
       </c>
       <c r="Q11" t="n">
-        <v>347</v>
+        <v>569</v>
       </c>
       <c r="R11" t="n">
-        <v>543</v>
+        <v>2008</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,115 +1490,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1845496295</t>
+          <t>1206618438</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845496295</t>
+          <t>https://m.place.naver.com/place/1206618438</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>파인미필라테스</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>pilatesfindme@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1320-9500</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울 송파구 충민로2길 34 북일PLAZA 5층 501호, 501-1호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/pilatesfindme</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vq19</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>415</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>333</v>
-      </c>
-      <c r="R12" t="n">
-        <v>748</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1423651019</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1423651019</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/송파_PT.xlsx
+++ b/naver-place-crawler/results_health/송파_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q2" t="n">
         <v>392</v>
       </c>
       <c r="R2" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,41 +650,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>슈나이더짐 PT&amp;필라테스</t>
+          <t>씨엘필라테스 잠실새내점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>schneider-gym@naver.com</t>
+          <t>clpilates6@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1379-6625</t>
+          <t>0507-1336-6376</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
+          <t>서울 송파구 백제고분로7길 57 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/schneider-gym</t>
+          <t>https://blog.naver.com/clpilates6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40v0r</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>408</v>
+        <v>742</v>
       </c>
       <c r="Q3" t="n">
-        <v>1137</v>
+        <v>1525</v>
       </c>
       <c r="R3" t="n">
-        <v>1545</v>
+        <v>2267</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>37562355</t>
+          <t>1469498219</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37562355</t>
+          <t>https://m.place.naver.com/place/1469498219</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -838,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -910,10 +914,10 @@
         <v>211</v>
       </c>
       <c r="Q5" t="n">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="R5" t="n">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -932,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -944,29 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피지오로직 재활PT&amp;트레이닝센터</t>
+          <t>슈나이더짐 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>physio_logic_@naver.com</t>
+          <t>schneider-gym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1357-7813</t>
+          <t>0507-1379-6625</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 99 601호</t>
+          <t>서울특별시 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/physio_logic_</t>
+          <t>https://blog.naver.com/schneider-gym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1001,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="Q6" t="n">
-        <v>302</v>
+        <v>1137</v>
       </c>
       <c r="R6" t="n">
-        <v>383</v>
+        <v>1545</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2067533579</t>
+          <t>37562355</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067533579</t>
+          <t>https://m.place.naver.com/place/37562355</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>앵글짐&amp;프리모필라테스</t>
+          <t>피지오로직 재활PT&amp;트레이닝센터</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>anglegym@naver.com</t>
+          <t>physio_logic_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1362-3197</t>
+          <t>0507-1357-7813</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
+          <t>서울특별시 송파구 가락로 99 601호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anglegym_primopilates/</t>
+          <t>https://blog.naver.com/physio_logic_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,7 +1079,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1095,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Q7" t="n">
-        <v>343</v>
+        <v>302</v>
       </c>
       <c r="R7" t="n">
-        <v>751</v>
+        <v>383</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,51 +1114,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1884191160</t>
+          <t>2067533579</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884191160</t>
+          <t>https://m.place.naver.com/place/2067533579</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>요가랩 잠실센터</t>
+          <t>앵글짐&amp;프리모필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>yogalab_jamsil@naver.com</t>
+          <t>anglegym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1347-9642</t>
+          <t>0507-1362-3197</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
+          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yogalab_jamsil</t>
+          <t>https://www.instagram.com/anglegym_primopilates/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,19 +1173,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43xv0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>163</v>
+        <v>410</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>344</v>
       </c>
       <c r="R8" t="n">
-        <v>183</v>
+        <v>754</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,51 +1208,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>38531279</t>
+          <t>1884191160</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38531279</t>
+          <t>https://m.place.naver.com/place/1884191160</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐타임 송파나루역점</t>
+          <t>요가랩 잠실센터</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymtime02@naver.com</t>
+          <t>yogalab_jamsil@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1409-7458</t>
+          <t>0507-1347-9642</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로 460 B1층</t>
+          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymtime02</t>
+          <t>https://blog.naver.com/yogalab_jamsil</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1272,13 +1272,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43xv0</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1287,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2759</v>
+        <v>163</v>
       </c>
       <c r="Q9" t="n">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
-        <v>3145</v>
+        <v>183</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,51 +1306,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1324257365</t>
+          <t>38531279</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324257365</t>
+          <t>https://m.place.naver.com/place/38531279</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐퍼스트 헬스&amp;PT 문정역점</t>
+          <t>더메이트 PT 문정점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cjh23032@naver.com</t>
+          <t>themate1907@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1371-9308</t>
+          <t>0507-1433-1907</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 법원로 114 엠스테이트 빌딩 B동 2층</t>
+          <t>서울특별시 송파구 법원로4길 10 힐스테이트에코문정 2층 215,218,219호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cjh23032</t>
+          <t>https://blog.naver.com/themate1907</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>697</v>
+        <v>156</v>
       </c>
       <c r="Q10" t="n">
-        <v>895</v>
+        <v>150</v>
       </c>
       <c r="R10" t="n">
-        <v>1592</v>
+        <v>306</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,56 +1400,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>313691459</t>
+          <t>1832145060</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/313691459</t>
+          <t>https://m.place.naver.com/place/1832145060</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이블짐 잠실역점</t>
+          <t>파인미필라테스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ablegym38@naver.com</t>
+          <t>pilatesfindme@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1360-6852</t>
+          <t>0507-1320-9500</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 올림픽로35가길 11 지하1층 001호</t>
+          <t>서울 송파구 충민로2길 34 북일PLAZA 5층 501호, 501-1호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://ablegym-jamsil-vrtour.netlify.app/</t>
+          <t>https://blog.naver.com/pilatesfindme</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1455,15 +1459,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vq19</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1475,13 +1483,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1439</v>
+        <v>419</v>
       </c>
       <c r="Q11" t="n">
-        <v>569</v>
+        <v>336</v>
       </c>
       <c r="R11" t="n">
-        <v>2008</v>
+        <v>755</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,17 +1498,111 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1206618438</t>
+          <t>1423651019</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206618438</t>
+          <t>https://m.place.naver.com/place/1423651019</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>리라이프짐 PT 방이점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>relifegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1395-7091</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 백제고분로50길 4 3층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/relifegym</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>308</v>
+      </c>
+      <c r="R12" t="n">
+        <v>537</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1878377486</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1878377486</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/송파_PT.xlsx
+++ b/naver-place-crawler/results_health/송파_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨엘필라테스 잠실새내점</t>
+          <t>발란아워 GYM&amp;PT 잠실점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>clpilates6@naver.com</t>
+          <t>balanour@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1336-6376</t>
+          <t>0507-1348-9763</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 송파구 백제고분로7길 57 7층</t>
+          <t>서울 송파구 백제고분로7길 53 B1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/clpilates6</t>
+          <t>https://blog.naver.com/balanour</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40v0r</t>
+          <t>https://talk.naver.com/ct/w45200</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>742</v>
+        <v>308</v>
       </c>
       <c r="Q3" t="n">
-        <v>1525</v>
+        <v>621</v>
       </c>
       <c r="R3" t="n">
-        <v>2267</v>
+        <v>929</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1469498219</t>
+          <t>1805832183</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1469498219</t>
+          <t>https://m.place.naver.com/place/1805832183</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>발란아워 GYM&amp;PT 잠실점</t>
+          <t>데일리피트니스 PT 개롱역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>balanour@naver.com</t>
+          <t>dailyfitness_1st@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1348-9763</t>
+          <t>0507-1402-1181</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
+          <t>서울 송파구 동남로 202 지하1층 데일리피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balanour</t>
+          <t>https://blog.naver.com/dailyfitness_1st</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4w9q8</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>308</v>
+        <v>211</v>
       </c>
       <c r="Q4" t="n">
-        <v>621</v>
+        <v>571</v>
       </c>
       <c r="R4" t="n">
-        <v>929</v>
+        <v>782</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1805832183</t>
+          <t>1135202102</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805832183</t>
+          <t>https://m.place.naver.com/place/1135202102</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>데일리피트니스 PT 개롱역점</t>
+          <t>슈나이더짐 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dailyfitness_1st@naver.com</t>
+          <t>schneider-gym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1402-1181</t>
+          <t>0507-1379-6625</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 동남로 202 지하1층 데일리피트니스</t>
+          <t>서울 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailyfitness_1st</t>
+          <t>https://blog.naver.com/schneider-gym</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4zi76</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>211</v>
+        <v>408</v>
       </c>
       <c r="Q5" t="n">
-        <v>570</v>
+        <v>1137</v>
       </c>
       <c r="R5" t="n">
-        <v>781</v>
+        <v>1545</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1135202102</t>
+          <t>37562355</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135202102</t>
+          <t>https://m.place.naver.com/place/37562355</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>슈나이더짐 PT&amp;필라테스</t>
+          <t>피지오로직 재활PT&amp;트레이닝센터</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>schneider-gym@naver.com</t>
+          <t>physio_logic_@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1379-6625</t>
+          <t>0507-1357-7813</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
+          <t>서울 송파구 가락로 99 601호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/schneider-gym</t>
+          <t>https://blog.naver.com/physio_logic_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -990,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wfd65</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1005,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Q6" t="n">
-        <v>1137</v>
+        <v>302</v>
       </c>
       <c r="R6" t="n">
-        <v>1545</v>
+        <v>383</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37562355</t>
+          <t>2067533579</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37562355</t>
+          <t>https://m.place.naver.com/place/2067533579</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1042,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피지오로직 재활PT&amp;트레이닝센터</t>
+          <t>앵글짐&amp;프리모필라테스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>physio_logic_@naver.com</t>
+          <t>anglegym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1357-7813</t>
+          <t>0507-1362-3197</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 99 601호</t>
+          <t>서울 송파구 가락로 151 동원빌딩 B1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/physio_logic_</t>
+          <t>https://www.instagram.com/anglegym_primopilates/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1079,15 +1091,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5txg6</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1099,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="Q7" t="n">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="R7" t="n">
-        <v>383</v>
+        <v>754</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2067533579</t>
+          <t>1884191160</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067533579</t>
+          <t>https://m.place.naver.com/place/1884191160</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1131,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>앵글짐&amp;프리모필라테스</t>
+          <t>요가랩 잠실센터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>anglegym@naver.com</t>
+          <t>yogalab_jamsil@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1362-3197</t>
+          <t>0507-1347-9642</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
+          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anglegym_primopilates/</t>
+          <t>https://blog.naver.com/yogalab_jamsil</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1173,15 +1189,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43xv0</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1193,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>410</v>
+        <v>163</v>
       </c>
       <c r="Q8" t="n">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
-        <v>754</v>
+        <v>183</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1884191160</t>
+          <t>38531279</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884191160</t>
+          <t>https://m.place.naver.com/place/38531279</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1225,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>요가랩 잠실센터</t>
+          <t>짐타임 송파나루역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>yogalab_jamsil@naver.com</t>
+          <t>gymtime02@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1347-9642</t>
+          <t>0507-1409-7458</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
+          <t>서울 송파구 백제고분로 460 B1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yogalab_jamsil</t>
+          <t>https://blog.naver.com/gymtime02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1277,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43xv0</t>
+          <t>https://talk.naver.com/ct/w7vk1pp</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1291,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>163</v>
+        <v>2764</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>386</v>
       </c>
       <c r="R9" t="n">
-        <v>183</v>
+        <v>3150</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>38531279</t>
+          <t>1324257365</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38531279</t>
+          <t>https://m.place.naver.com/place/1324257365</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1323,39 +1343,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더메이트 PT 문정점</t>
+          <t>에이블짐 잠실역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>themate1907@naver.com</t>
+          <t>ablegym38@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1433-1907</t>
+          <t>0507-1360-6852</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 법원로4길 10 힐스테이트에코문정 2층 215,218,219호</t>
+          <t>서울 송파구 올림픽로35가길 11 지하1층 001호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/themate1907</t>
+          <t>https://ablegym-jamsil-vrtour.netlify.app/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1365,15 +1385,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41l40</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1385,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>156</v>
+        <v>1438</v>
       </c>
       <c r="Q10" t="n">
-        <v>150</v>
+        <v>569</v>
       </c>
       <c r="R10" t="n">
-        <v>306</v>
+        <v>2007</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1832145060</t>
+          <t>1206618438</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1832145060</t>
+          <t>https://m.place.naver.com/place/1206618438</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1417,34 +1441,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>파인미필라테스</t>
+          <t>더메이트 PT 문정점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pilatesfindme@naver.com</t>
+          <t>themate1907@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1320-9500</t>
+          <t>0507-1433-1907</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 송파구 충민로2길 34 북일PLAZA 5층 501호, 501-1호</t>
+          <t>서울 송파구 법원로4길 10 힐스테이트에코문정 2층 215,218,219호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilatesfindme</t>
+          <t>https://blog.naver.com/themate1907</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1469,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vq19</t>
+          <t>https://talk.naver.com/ct/w5zhme</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1483,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>419</v>
+        <v>156</v>
       </c>
       <c r="Q11" t="n">
-        <v>336</v>
+        <v>150</v>
       </c>
       <c r="R11" t="n">
-        <v>755</v>
+        <v>306</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1498,109 +1522,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1423651019</t>
+          <t>1832145060</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1423651019</t>
+          <t>https://m.place.naver.com/place/1832145060</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>리라이프짐 PT 방이점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>relifegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1395-7091</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울특별시 송파구 백제고분로50길 4 3층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/relifegym</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>229</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>308</v>
-      </c>
-      <c r="R12" t="n">
-        <v>537</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1878377486</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1878377486</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/송파_PT.xlsx
+++ b/naver-place-crawler/results_health/송파_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>모어핏 여성전용 PT&amp;Pilates 송파나루점</t>
+          <t>씨엘필라테스 잠실새내점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>more_fit@naver.com</t>
+          <t>clpilates6@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1395-4335</t>
+          <t>0507-1336-6376</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울 송파구 백제고분로 433 5층</t>
+          <t>서울 송파구 백제고분로7길 57 7층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/more_fit</t>
+          <t>https://blog.naver.com/clpilates6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cku7</t>
+          <t>https://talk.naver.com/ct/w40v0r</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>207</v>
+        <v>742</v>
       </c>
       <c r="Q2" t="n">
-        <v>392</v>
+        <v>1531</v>
       </c>
       <c r="R2" t="n">
-        <v>599</v>
+        <v>2273</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1034357419</t>
+          <t>1469498219</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034357419</t>
+          <t>https://m.place.naver.com/place/1469498219</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨엘필라테스 잠실새내점</t>
+          <t>LX 피트니스 24시 헬스 잠실본점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>clpilates6@naver.com</t>
+          <t>lxfitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1336-6376</t>
+          <t>0507-1417-1044</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 송파구 백제고분로7길 57 7층</t>
+          <t>서울특별시 송파구 백제고분로 122 월드센터 2층 LX피트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/clpilates6</t>
+          <t>https://www.youtube.com/@ng-962</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +699,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40v0r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>742</v>
+        <v>937</v>
       </c>
       <c r="Q3" t="n">
-        <v>1530</v>
+        <v>500</v>
       </c>
       <c r="R3" t="n">
-        <v>2272</v>
+        <v>1437</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1469498219</t>
+          <t>1339944668</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1469498219</t>
+          <t>https://m.place.naver.com/place/1339944668</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -842,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -936,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1026,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1120,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1214,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1312,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1410,41 +1406,41 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>파인미필라테스</t>
+          <t>모어핏 여성전용 PT&amp;Pilates 송파나루점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pilatesfindme@naver.com</t>
+          <t>more_fit@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1320-9500</t>
+          <t>0507-1395-4335</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 송파구 충민로2길 34 북일PLAZA 5층 501호, 501-1호</t>
+          <t>서울 송파구 백제고분로 433 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilatesfindme</t>
+          <t>https://blog.naver.com/more_fit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1469,7 +1465,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vq19</t>
+          <t>https://talk.naver.com/ct/w4cku7</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1483,13 +1479,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>419</v>
+        <v>207</v>
       </c>
       <c r="Q11" t="n">
-        <v>336</v>
+        <v>392</v>
       </c>
       <c r="R11" t="n">
-        <v>755</v>
+        <v>599</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1498,17 +1494,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1423651019</t>
+          <t>1034357419</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1423651019</t>
+          <t>https://m.place.naver.com/place/1034357419</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/송파_PT.xlsx
+++ b/naver-place-crawler/results_health/송파_PT.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -628,10 +628,10 @@
         <v>742</v>
       </c>
       <c r="Q2" t="n">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="R2" t="n">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LX 피트니스 24시 헬스 잠실본점</t>
+          <t>데일리피트니스 PT 개롱역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lxfitness@naver.com</t>
+          <t>dailyfitness_1st@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1417-1044</t>
+          <t>0507-1402-1181</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로 122 월드센터 2층 LX피트니스</t>
+          <t>서울특별시 송파구 동남로 202 지하1층 데일리피트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ng-962</t>
+          <t>https://blog.naver.com/dailyfitness_1st</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>937</v>
+        <v>211</v>
       </c>
       <c r="Q3" t="n">
-        <v>500</v>
+        <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>1437</v>
+        <v>783</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1339944668</t>
+          <t>1135202102</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1339944668</t>
+          <t>https://m.place.naver.com/place/1135202102</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>데일리피트니스 PT 개롱역점</t>
+          <t>발란아워 GYM&amp;PT 잠실점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dailyfitness_1st@naver.com</t>
+          <t>balanour@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1402-1181</t>
+          <t>0507-1348-9763</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 동남로 202 지하1층 데일리피트니스</t>
+          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailyfitness_1st</t>
+          <t>https://blog.naver.com/balanour</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>211</v>
+        <v>308</v>
       </c>
       <c r="Q4" t="n">
-        <v>571</v>
+        <v>622</v>
       </c>
       <c r="R4" t="n">
-        <v>782</v>
+        <v>930</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1135202102</t>
+          <t>1805832183</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135202102</t>
+          <t>https://m.place.naver.com/place/1805832183</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>발란아워 GYM&amp;PT 잠실점</t>
+          <t>앵글짐&amp;프리모필라테스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>balanour@naver.com</t>
+          <t>anglegym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1348-9763</t>
+          <t>0507-1362-3197</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
+          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balanour</t>
+          <t>https://www.instagram.com/anglegym_primopilates/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>308</v>
+        <v>411</v>
       </c>
       <c r="Q5" t="n">
-        <v>621</v>
+        <v>344</v>
       </c>
       <c r="R5" t="n">
-        <v>929</v>
+        <v>755</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1805832183</t>
+          <t>1884191160</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805832183</t>
+          <t>https://m.place.naver.com/place/1884191160</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1038,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>앵글짐&amp;프리모필라테스</t>
+          <t>피지오로직 재활PT&amp;트레이닝센터</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>anglegym@naver.com</t>
+          <t>physio_logic_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1362-3197</t>
+          <t>0507-1357-7813</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
+          <t>서울특별시 송파구 가락로 99 601호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anglegym_primopilates/</t>
+          <t>https://blog.naver.com/physio_logic_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="Q7" t="n">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="R7" t="n">
-        <v>755</v>
+        <v>383</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1884191160</t>
+          <t>2067533579</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884191160</t>
+          <t>https://m.place.naver.com/place/2067533579</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1127,34 +1127,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피지오로직 재활PT&amp;트레이닝센터</t>
+          <t>요가랩 잠실센터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>physio_logic_@naver.com</t>
+          <t>yogalab_jamsil@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1357-7813</t>
+          <t>0507-1347-9642</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 99 601호</t>
+          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/physio_logic_</t>
+          <t>https://blog.naver.com/yogalab_jamsil</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1174,10 +1174,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43xv0</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="Q8" t="n">
-        <v>302</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
-        <v>383</v>
+        <v>183</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1208,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2067533579</t>
+          <t>38531279</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067533579</t>
+          <t>https://m.place.naver.com/place/38531279</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1225,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>요가랩 잠실센터</t>
+          <t>짐타임 송파나루역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>yogalab_jamsil@naver.com</t>
+          <t>gymtime02@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1347-9642</t>
+          <t>0507-1409-7458</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
+          <t>서울특별시 송파구 백제고분로 460 B1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yogalab_jamsil</t>
+          <t>https://blog.naver.com/gymtime02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1268,17 +1272,13 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43xv0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>163</v>
+        <v>2771</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>386</v>
       </c>
       <c r="R9" t="n">
-        <v>183</v>
+        <v>3157</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>38531279</t>
+          <t>1324257365</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38531279</t>
+          <t>https://m.place.naver.com/place/1324257365</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1324,34 +1324,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐타임 송파나루역점</t>
+          <t>에이블짐 잠실역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gymtime02@naver.com</t>
+          <t>ablegym38@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1409-7458</t>
+          <t>0507-1360-6852</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로 460 B1층</t>
+          <t>서울특별시 송파구 올림픽로35가길 11 지하1층 001호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymtime02</t>
+          <t>https://ablegym-jamsil-vrtour.netlify.app/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1372,7 +1372,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2771</v>
+        <v>1438</v>
       </c>
       <c r="Q10" t="n">
-        <v>386</v>
+        <v>569</v>
       </c>
       <c r="R10" t="n">
-        <v>3157</v>
+        <v>2007</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1324257365</t>
+          <t>1206618438</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324257365</t>
+          <t>https://m.place.naver.com/place/1206618438</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1418,29 +1418,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모어핏 여성전용 PT&amp;Pilates 송파나루점</t>
+          <t>더메이트 PT 문정점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>more_fit@naver.com</t>
+          <t>themate1907@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1395-4335</t>
+          <t>0507-1433-1907</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 송파구 백제고분로 433 5층</t>
+          <t>서울특별시 송파구 법원로4길 10 힐스테이트에코문정 2층 215,218,219호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/more_fit</t>
+          <t>https://blog.naver.com/themate1907</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1460,14 +1460,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4cku7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1479,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="Q11" t="n">
-        <v>392</v>
+        <v>151</v>
       </c>
       <c r="R11" t="n">
-        <v>599</v>
+        <v>307</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,12 +1490,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1034357419</t>
+          <t>1832145060</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034357419</t>
+          <t>https://m.place.naver.com/place/1832145060</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/송파_PT.xlsx
+++ b/naver-place-crawler/results_health/송파_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>씨엘필라테스 잠실새내점</t>
+          <t>모어핏 여성전용 PT&amp;Pilates 송파나루점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>clpilates6@naver.com</t>
+          <t>more_fit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1336-6376</t>
+          <t>0507-1395-4335</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울 송파구 백제고분로7길 57 7층</t>
+          <t>서울 송파구 백제고분로 433 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/clpilates6</t>
+          <t>https://blog.naver.com/more_fit</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40v0r</t>
+          <t>https://talk.naver.com/ct/w4cku7</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>742</v>
+        <v>207</v>
       </c>
       <c r="Q2" t="n">
-        <v>1533</v>
+        <v>392</v>
       </c>
       <c r="R2" t="n">
-        <v>2275</v>
+        <v>599</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1469498219</t>
+          <t>1034357419</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1469498219</t>
+          <t>https://m.place.naver.com/place/1034357419</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>데일리피트니스 PT 개롱역점</t>
+          <t>씨엘필라테스 잠실새내점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dailyfitness_1st@naver.com</t>
+          <t>clpilates6@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1402-1181</t>
+          <t>0507-1336-6376</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 동남로 202 지하1층 데일리피트니스</t>
+          <t>서울 송파구 백제고분로7길 57 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailyfitness_1st</t>
+          <t>https://blog.naver.com/clpilates6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40v0r</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>211</v>
+        <v>743</v>
       </c>
       <c r="Q3" t="n">
-        <v>572</v>
+        <v>1530</v>
       </c>
       <c r="R3" t="n">
-        <v>783</v>
+        <v>2273</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1135202102</t>
+          <t>1469498219</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135202102</t>
+          <t>https://m.place.naver.com/place/1469498219</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>발란아워 GYM&amp;PT 잠실점</t>
+          <t>데일리피트니스 PT 개롱역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>balanour@naver.com</t>
+          <t>dailyfitness_1st@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1348-9763</t>
+          <t>0507-1402-1181</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
+          <t>서울특별시 송파구 동남로 202 지하1층 데일리피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balanour</t>
+          <t>https://blog.naver.com/dailyfitness_1st</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -813,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>308</v>
+        <v>211</v>
       </c>
       <c r="Q4" t="n">
-        <v>622</v>
+        <v>572</v>
       </c>
       <c r="R4" t="n">
-        <v>930</v>
+        <v>783</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1805832183</t>
+          <t>1135202102</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805832183</t>
+          <t>https://m.place.naver.com/place/1135202102</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>앵글짐&amp;프리모필라테스</t>
+          <t>발란아워 GYM&amp;PT 잠실점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>anglegym@naver.com</t>
+          <t>balanour@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1362-3197</t>
+          <t>0507-1348-9763</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
+          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anglegym_primopilates/</t>
+          <t>https://blog.naver.com/balanour</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -907,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="Q5" t="n">
-        <v>344</v>
+        <v>622</v>
       </c>
       <c r="R5" t="n">
-        <v>755</v>
+        <v>930</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1884191160</t>
+          <t>1805832183</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884191160</t>
+          <t>https://m.place.naver.com/place/1805832183</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,29 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>슈나이더짐 PT&amp;필라테스</t>
+          <t>앵글짐&amp;프리모필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>schneider-gym@naver.com</t>
+          <t>anglegym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1379-6625</t>
+          <t>0507-1362-3197</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
+          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/schneider-gym</t>
+          <t>https://www.instagram.com/anglegym_primopilates/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -981,7 +985,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1001,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Q6" t="n">
-        <v>1137</v>
+        <v>344</v>
       </c>
       <c r="R6" t="n">
-        <v>1545</v>
+        <v>755</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1020,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37562355</t>
+          <t>1884191160</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37562355</t>
+          <t>https://m.place.naver.com/place/1884191160</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피지오로직 재활PT&amp;트레이닝센터</t>
+          <t>슈나이더짐 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>physio_logic_@naver.com</t>
+          <t>schneider-gym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1357-7813</t>
+          <t>0507-1379-6625</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 99 601호</t>
+          <t>서울특별시 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/physio_logic_</t>
+          <t>https://blog.naver.com/schneider-gym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1095,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="Q7" t="n">
-        <v>302</v>
+        <v>1137</v>
       </c>
       <c r="R7" t="n">
-        <v>383</v>
+        <v>1545</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1114,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2067533579</t>
+          <t>37562355</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067533579</t>
+          <t>https://m.place.naver.com/place/37562355</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1127,44 +1131,48 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>요가랩 잠실센터</t>
+          <t>씨케이짐 PT&amp;헬스 문정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>yogalab_jamsil@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>ck_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ceo@ckgym.kr</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1347-9642</t>
+          <t>0507-1379-2514</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
+          <t>서울특별시 송파구 새말로 128 B1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yogalab_jamsil</t>
+          <t>https://ckgym.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1174,17 +1182,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43xv0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1193,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>163</v>
+        <v>2202</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>726</v>
       </c>
       <c r="R8" t="n">
-        <v>183</v>
+        <v>2928</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1212,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>38531279</t>
+          <t>1204361368</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38531279</t>
+          <t>https://m.place.naver.com/place/1204361368</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1290,10 +1294,10 @@
         <v>2771</v>
       </c>
       <c r="Q9" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="R9" t="n">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1319,44 +1323,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이블짐 잠실역점</t>
+          <t>더메이트 PT 문정점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ablegym38@naver.com</t>
+          <t>themate1907@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1360-6852</t>
+          <t>0507-1433-1907</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 올림픽로35가길 11 지하1층 001호</t>
+          <t>서울특별시 송파구 법원로4길 10 힐스테이트에코문정 2층 215,218,219호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://ablegym-jamsil-vrtour.netlify.app/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1366,10 +1370,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zhme</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1381,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1438</v>
+        <v>156</v>
       </c>
       <c r="Q10" t="n">
-        <v>569</v>
+        <v>152</v>
       </c>
       <c r="R10" t="n">
-        <v>2007</v>
+        <v>308</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1404,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1206618438</t>
+          <t>1832145060</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206618438</t>
+          <t>https://m.place.naver.com/place/1832145060</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1418,29 +1426,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더메이트 PT 문정점</t>
+          <t>짐구석피티 위례점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>themate1907@naver.com</t>
+          <t>gymgooseok1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1433-1907</t>
+          <t>0507-1465-0342</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 법원로4길 10 힐스테이트에코문정 2층 215,218,219호</t>
+          <t>서울특별시 송파구 위례광장로 200 10층 제1002호, 제1003호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/themate1907</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1450,20 +1458,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45bds</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1475,13 +1487,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="Q11" t="n">
-        <v>151</v>
+        <v>346</v>
       </c>
       <c r="R11" t="n">
-        <v>307</v>
+        <v>541</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,15 +1502,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1832145060</t>
+          <t>1845496295</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1832145060</t>
+          <t>https://m.place.naver.com/place/1845496295</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>파인미필라테스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pilatesfindme@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1320-9500</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울 송파구 충민로2길 34 북일PLAZA 5층 501호, 501-1호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pilatesfindme</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vq19</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>419</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>337</v>
+      </c>
+      <c r="R12" t="n">
+        <v>756</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1423651019</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1423651019</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/송파_PT.xlsx
+++ b/naver-place-crawler/results_health/송파_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -726,10 +726,10 @@
         <v>743</v>
       </c>
       <c r="Q3" t="n">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="R3" t="n">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -820,10 +820,10 @@
         <v>211</v>
       </c>
       <c r="Q4" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="R4" t="n">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1200,10 +1200,10 @@
         <v>2202</v>
       </c>
       <c r="Q8" t="n">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="R8" t="n">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1234,29 +1234,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐타임 송파나루역점</t>
+          <t>투엑스휘트니스 잠실점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymtime02@naver.com</t>
+          <t>hik8891@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1409-7458</t>
+          <t>0507-1447-9811</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로 460 B1층</t>
+          <t>서울특별시 송파구 올림픽로 145 리센츠 상가 B1층 잠실새내역 8번출구</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymtime02</t>
+          <t>https://www.instagram.com/2x_fitness_jamsil_/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1282,7 +1282,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2771</v>
+        <v>1756</v>
       </c>
       <c r="Q9" t="n">
-        <v>387</v>
+        <v>180</v>
       </c>
       <c r="R9" t="n">
-        <v>3158</v>
+        <v>1936</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,51 +1306,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1324257365</t>
+          <t>34897496</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324257365</t>
+          <t>https://m.place.naver.com/place/34897496</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더메이트 PT 문정점</t>
+          <t>파인미필라테스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>themate1907@naver.com</t>
+          <t>pilatesfindme@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1433-1907</t>
+          <t>0507-1320-9500</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 법원로4길 10 힐스테이트에코문정 2층 215,218,219호</t>
+          <t>서울 송파구 충민로2길 34 북일PLAZA 5층 501호, 501-1호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/pilatesfindme</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zhme</t>
+          <t>https://talk.naver.com/ct/w5vq19</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>156</v>
+        <v>419</v>
       </c>
       <c r="Q10" t="n">
-        <v>152</v>
+        <v>337</v>
       </c>
       <c r="R10" t="n">
-        <v>308</v>
+        <v>756</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,61 +1404,61 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1832145060</t>
+          <t>1423651019</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1832145060</t>
+          <t>https://m.place.naver.com/place/1423651019</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내체육관</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐구석피티 위례점</t>
+          <t>에이투에프 송파</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gymgooseok1@naver.com</t>
+          <t>af0168@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1465-0342</t>
+          <t>0507-1356-8879</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 위례광장로 200 10층 제1002호, 제1003호</t>
+          <t>서울 송파구 위례성대로 180 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://a2f.co.kr/trial-reservation.html</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45bds</t>
+          <t>https://talk.naver.com/ct/w9ficj0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1483,17 +1483,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="Q11" t="n">
-        <v>346</v>
+        <v>260</v>
       </c>
       <c r="R11" t="n">
-        <v>541</v>
+        <v>438</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1502,51 +1502,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1845496295</t>
+          <t>36208743</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845496295</t>
+          <t>https://m.place.naver.com/place/36208743</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>파인미필라테스</t>
+          <t>피티라이프 PT 삼전점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pilatesfindme@naver.com</t>
+          <t>ptlife2026@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1320-9500</t>
+          <t>0507-1445-2850</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울 송파구 충민로2길 34 북일PLAZA 5층 501호, 501-1호</t>
+          <t>서울특별시 송파구 백제고분로21길 38 2층 201호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilatesfindme</t>
+          <t>https://blog.naver.com/ptlife2026/224151306548</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1566,14 +1566,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vq19</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1585,13 +1581,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>419</v>
+        <v>19</v>
       </c>
       <c r="Q12" t="n">
-        <v>337</v>
+        <v>68</v>
       </c>
       <c r="R12" t="n">
-        <v>756</v>
+        <v>87</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1600,17 +1596,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1423651019</t>
+          <t>2002715175</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1423651019</t>
+          <t>https://m.place.naver.com/place/2002715175</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/송파_PT.xlsx
+++ b/naver-place-crawler/results_health/송파_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -726,10 +726,10 @@
         <v>743</v>
       </c>
       <c r="Q3" t="n">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="R3" t="n">
-        <v>2274</v>
+        <v>2278</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="R4" t="n">
         <v>784</v>
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>발란아워 GYM&amp;PT 잠실점</t>
+          <t>앵글짐&amp;프리모필라테스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>balanour@naver.com</t>
+          <t>anglegym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1348-9763</t>
+          <t>0507-1362-3197</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
+          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balanour</t>
+          <t>https://www.instagram.com/anglegym_primopilates/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>308</v>
+        <v>411</v>
       </c>
       <c r="Q5" t="n">
-        <v>622</v>
+        <v>344</v>
       </c>
       <c r="R5" t="n">
-        <v>930</v>
+        <v>755</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1805832183</t>
+          <t>1884191160</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805832183</t>
+          <t>https://m.place.naver.com/place/1884191160</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,29 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>앵글짐&amp;프리모필라테스</t>
+          <t>발란아워 GYM&amp;PT 잠실점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>anglegym@naver.com</t>
+          <t>balanour@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1362-3197</t>
+          <t>0507-1348-9763</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
+          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anglegym_primopilates/</t>
+          <t>https://blog.naver.com/balanour</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="Q6" t="n">
-        <v>344</v>
+        <v>624</v>
       </c>
       <c r="R6" t="n">
-        <v>755</v>
+        <v>932</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1884191160</t>
+          <t>1805832183</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884191160</t>
+          <t>https://m.place.naver.com/place/1805832183</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         <v>2202</v>
       </c>
       <c r="Q8" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="R8" t="n">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 올림픽로 145 리센츠 상가 B1층 잠실새내역 8번출구</t>
+          <t>서울 송파구 올림픽로 145 리센츠 상가 B1층 잠실새내역 8번출구</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1276,10 +1276,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4nxmm</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1291,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="Q9" t="n">
         <v>180</v>
       </c>
       <c r="R9" t="n">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1323,34 +1327,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>파인미필라테스</t>
+          <t>요가랩 잠실센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pilatesfindme@naver.com</t>
+          <t>yogalab_jamsil@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1320-9500</t>
+          <t>0507-1347-9642</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 송파구 충민로2길 34 북일PLAZA 5층 501호, 501-1호</t>
+          <t>서울 송파구 송파대로 562 웰리스타워 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilatesfindme</t>
+          <t>https://blog.naver.com/yogalab_jamsil</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1375,7 +1379,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vq19</t>
+          <t>https://talk.naver.com/ct/w43xv0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1389,13 +1393,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>419</v>
+        <v>163</v>
       </c>
       <c r="Q10" t="n">
-        <v>337</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>756</v>
+        <v>183</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,12 +1408,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1423651019</t>
+          <t>38531279</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1423651019</t>
+          <t>https://m.place.naver.com/place/38531279</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1421,39 +1425,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>실내체육관</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이투에프 송파</t>
+          <t>짐타임 송파나루역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>af0168@naver.com</t>
+          <t>gymtime02@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1356-8879</t>
+          <t>0507-1409-7458</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 송파구 위례성대로 180 지하1층</t>
+          <t>서울특별시 송파구 백제고분로 460 B1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://a2f.co.kr/trial-reservation.html</t>
+          <t>https://blog.naver.com/gymtime02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1463,37 +1467,33 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9ficj0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>178</v>
+        <v>2777</v>
       </c>
       <c r="Q11" t="n">
-        <v>260</v>
+        <v>387</v>
       </c>
       <c r="R11" t="n">
-        <v>438</v>
+        <v>3164</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1502,109 +1502,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>36208743</t>
+          <t>1324257365</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36208743</t>
+          <t>https://m.place.naver.com/place/1324257365</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>피티라이프 PT 삼전점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ptlife2026@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1445-2850</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울특별시 송파구 백제고분로21길 38 2층 201호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/ptlife2026/224151306548</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>68</v>
-      </c>
-      <c r="R12" t="n">
-        <v>87</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2002715175</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2002715175</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/송파_PT.xlsx
+++ b/naver-place-crawler/results_health/송파_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -650,41 +650,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨엘필라테스 잠실새내점</t>
+          <t>트렌디우먼휘트니스 거여역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>clpilates6@naver.com</t>
+          <t>trendywm3@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1336-6376</t>
+          <t>02-409-8885</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 송파구 백제고분로7길 57 7층</t>
+          <t>서울특별시 송파구 오금로 516 B1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/clpilates6</t>
+          <t>https://www.instagram.com/trendywomon_gy</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +699,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40v0r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>743</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1535</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>2278</v>
+        <v>23</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1469498219</t>
+          <t>2094681572</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1469498219</t>
+          <t>https://m.place.naver.com/place/2094681572</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -760,34 +756,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>데일리피트니스 PT 개롱역점</t>
+          <t>좋은습관 PT STUDIO 문정</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dailyfitness_1st@naver.com</t>
+          <t>auth-letic_couple@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1402-1181</t>
+          <t>0507-1315-4024</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 동남로 202 지하1층 데일리피트니스</t>
+          <t>서울특별시 송파구 법원로4길 6 문정아이파크 지하1층 103, 104호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailyfitness_1st</t>
+          <t>https://naver.me/FpPu3Wkm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -797,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>212</v>
+        <v>586</v>
       </c>
       <c r="Q4" t="n">
-        <v>572</v>
+        <v>114</v>
       </c>
       <c r="R4" t="n">
-        <v>784</v>
+        <v>700</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1135202102</t>
+          <t>1123691340</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135202102</t>
+          <t>https://m.place.naver.com/place/1123691340</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -854,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>앵글짐&amp;프리모필라테스</t>
+          <t>데일리피트니스 PT 개롱역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>anglegym@naver.com</t>
+          <t>dailyfitness_1st@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1362-3197</t>
+          <t>0507-1402-1181</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
+          <t>서울특별시 송파구 동남로 202 지하1층 데일리피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anglegym_primopilates/</t>
+          <t>https://blog.naver.com/dailyfitness_1st</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -911,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>411</v>
+        <v>212</v>
       </c>
       <c r="Q5" t="n">
-        <v>344</v>
+        <v>573</v>
       </c>
       <c r="R5" t="n">
-        <v>755</v>
+        <v>785</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1884191160</t>
+          <t>1135202102</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884191160</t>
+          <t>https://m.place.naver.com/place/1135202102</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -948,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>발란아워 GYM&amp;PT 잠실점</t>
+          <t>앵글짐&amp;프리모필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>balanour@naver.com</t>
+          <t>anglegym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1348-9763</t>
+          <t>0507-1362-3197</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
+          <t>서울특별시 송파구 가락로 151 동원빌딩 B1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balanour</t>
+          <t>https://www.instagram.com/anglegym_primopilates/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,7 +981,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1005,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>308</v>
+        <v>411</v>
       </c>
       <c r="Q6" t="n">
-        <v>624</v>
+        <v>344</v>
       </c>
       <c r="R6" t="n">
-        <v>932</v>
+        <v>755</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1805832183</t>
+          <t>1884191160</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805832183</t>
+          <t>https://m.place.naver.com/place/1884191160</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1042,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>슈나이더짐 PT&amp;필라테스</t>
+          <t>발란아워 GYM&amp;PT 잠실점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>schneider-gym@naver.com</t>
+          <t>balanour@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1379-6625</t>
+          <t>0507-1348-9763</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
+          <t>서울특별시 송파구 백제고분로7길 53 B1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/schneider-gym</t>
+          <t>https://blog.naver.com/balanour</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1099,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>408</v>
+        <v>309</v>
       </c>
       <c r="Q7" t="n">
-        <v>1137</v>
+        <v>624</v>
       </c>
       <c r="R7" t="n">
-        <v>1545</v>
+        <v>933</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37562355</t>
+          <t>1805832183</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37562355</t>
+          <t>https://m.place.naver.com/place/1805832183</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1136,43 +1132,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>씨케이짐 PT&amp;헬스 문정점</t>
+          <t>슈나이더짐 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ck_gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ceo@ckgym.kr</t>
-        </is>
-      </c>
+          <t>schneider-gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1379-2514</t>
+          <t>0507-1379-6625</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 새말로 128 B1</t>
+          <t>서울특별시 송파구 동남로 110 3층~5층 슈나이더짐&amp;슈필라테스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://ckgym.co.kr/</t>
+          <t>https://blog.naver.com/schneider-gym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1188,7 +1180,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1197,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2202</v>
+        <v>408</v>
       </c>
       <c r="Q8" t="n">
-        <v>728</v>
+        <v>1137</v>
       </c>
       <c r="R8" t="n">
-        <v>2930</v>
+        <v>1545</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,81 +1204,81 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1204361368</t>
+          <t>37562355</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1204361368</t>
+          <t>https://m.place.naver.com/place/37562355</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>투엑스휘트니스 잠실점</t>
+          <t>씨케이짐 PT&amp;헬스 문정점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hik8891@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>ck_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ceo@ckgym.kr</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1447-9811</t>
+          <t>0507-1379-2514</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 송파구 올림픽로 145 리센츠 상가 B1층 잠실새내역 8번출구</t>
+          <t>서울특별시 송파구 새말로 128 B1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/2x_fitness_jamsil_/</t>
+          <t>https://ckgym.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4nxmm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1295,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1758</v>
+        <v>2202</v>
       </c>
       <c r="Q9" t="n">
-        <v>180</v>
+        <v>729</v>
       </c>
       <c r="R9" t="n">
-        <v>1938</v>
+        <v>2931</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,17 +1302,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>34897496</t>
+          <t>1204361368</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34897496</t>
+          <t>https://m.place.naver.com/place/1204361368</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1418,41 +1410,41 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐타임 송파나루역점</t>
+          <t>더메이트 PT 문정점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gymtime02@naver.com</t>
+          <t>themate1907@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1409-7458</t>
+          <t>0507-1433-1907</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 백제고분로 460 B1층</t>
+          <t>서울특별시 송파구 법원로4길 10 힐스테이트에코문정 2층 215,218,219호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymtime02</t>
+          <t>https://blog.naver.com/themate1907</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,7 +1470,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1487,13 +1479,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2777</v>
+        <v>156</v>
       </c>
       <c r="Q11" t="n">
-        <v>387</v>
+        <v>152</v>
       </c>
       <c r="R11" t="n">
-        <v>3164</v>
+        <v>308</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1502,17 +1494,205 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1324257365</t>
+          <t>1832145060</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324257365</t>
+          <t>https://m.place.naver.com/place/1832145060</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>블루베리짐</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>tldnjs9202@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1328-3218</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 석촌호수로 172 지하1층 블루베리짐</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tldnjs9202</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>56</v>
+      </c>
+      <c r="R12" t="n">
+        <v>122</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1343451311</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1343451311</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>짐구석피티 위례점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gymgooseok1@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1465-0342</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 위례광장로 200 10층 제1002호, 제1003호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymgooseok1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>346</v>
+      </c>
+      <c r="R13" t="n">
+        <v>541</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1845496295</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845496295</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
